--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_env_significance.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_env_significance.xlsx
@@ -471,17 +471,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.37 ± 0.93</t>
+          <t>7.78 ± 1.01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.81 ± 0.44</t>
+          <t>2.68 ± 0.57</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3.45 ± 0.69</t>
+          <t>3.82 ± 0.85</t>
         </is>
       </c>
     </row>
@@ -496,22 +496,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>p &lt; 0.05*</t>
+          <t>p &lt; 0.01**</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.07 ± 0.46</t>
+          <t>9.29 ± 0.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.12 ± 0.28</t>
+          <t>9.04 ± 0.31</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.34 ± 0.39</t>
+          <t>9.53 ± 0.44</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,17 +531,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.79 ± 0.33</t>
+          <t>18.92 ± 0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.13 ± 0.32</t>
+          <t>19.55 ± 0.45</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.25 ± 0.42</t>
+          <t>19.96 ± 0.79</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MPS (Phi)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -561,17 +561,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.83 ± 0.20</t>
+          <t>1.77 ± 0.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.28 ± 0.09</t>
+          <t>2.00 ± 0.38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.46 ± 0.16</t>
+          <t>2.27 ± 0.54</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>MPS (Phi)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -591,17 +591,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.64 ± 0.64</t>
+          <t>0.85 ± 0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.78 ± 0.35</t>
+          <t>1.34 ± 0.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.08 ± 0.62</t>
+          <t>1.37 ± 0.20</t>
         </is>
       </c>
     </row>
@@ -629,10 +629,10 @@
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_env_significance.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_env_significance.xlsx
@@ -471,17 +471,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.78 ± 1.01</t>
+          <t>8.21 ± 0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.68 ± 0.57</t>
+          <t>2.61 ± 0.45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3.82 ± 0.85</t>
+          <t>3.51 ± 0.73</t>
         </is>
       </c>
     </row>
@@ -496,22 +496,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>p &lt; 0.01**</t>
+          <t>p &lt; 0.05*</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.29 ± 0.49</t>
+          <t>9.12 ± 0.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.04 ± 0.31</t>
+          <t>9.14 ± 0.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.53 ± 0.44</t>
+          <t>9.31 ± 0.41</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,17 +531,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18.92 ± 0.63</t>
+          <t>1.79 ± 0.36</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.55 ± 0.45</t>
+          <t>2.16 ± 0.36</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.96 ± 0.79</t>
+          <t>2.25 ± 0.45</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>MPS (Phi)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -561,17 +561,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.77 ± 0.33</t>
+          <t>0.83 ± 0.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.00 ± 0.38</t>
+          <t>1.27 ± 0.10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2.27 ± 0.54</t>
+          <t>1.45 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MPS (Phi)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -591,17 +591,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.85 ± 0.20</t>
+          <t>18.80 ± 0.67</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.34 ± 0.11</t>
+          <t>19.72 ± 0.36</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.37 ± 0.20</t>
+          <t>20.04 ± 0.65</t>
         </is>
       </c>
     </row>
@@ -626,13 +626,13 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_env_significance.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_env_significance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,11 +449,6 @@
           <t>Cluster C2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster C3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -471,17 +466,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.21 ± 0.98</t>
+          <t>7.58 ± 1.08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.61 ± 0.45</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>3.51 ± 0.73</t>
+          <t>3.49 ± 0.56</t>
         </is>
       </c>
     </row>
@@ -501,17 +491,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.12 ± 0.49</t>
+          <t>9.10 ± 0.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.14 ± 0.30</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>9.31 ± 0.41</t>
+          <t>9.07 ± 0.24</t>
         </is>
       </c>
     </row>
@@ -531,17 +516,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.79 ± 0.36</t>
+          <t>1.73 ± 0.38</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.16 ± 0.36</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2.25 ± 0.45</t>
+          <t>1.98 ± 0.31</t>
         </is>
       </c>
     </row>
@@ -561,17 +541,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.83 ± 0.21</t>
+          <t>0.84 ± 0.23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.27 ± 0.10</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1.45 ± 0.17</t>
+          <t>1.32 ± 0.12</t>
         </is>
       </c>
     </row>
@@ -591,17 +566,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.80 ± 0.67</t>
+          <t>19.25 ± 0.62</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.72 ± 0.36</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>20.04 ± 0.65</t>
+          <t>19.89 ± 0.46</t>
         </is>
       </c>
     </row>
@@ -613,7 +583,6 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -626,13 +595,10 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
-      </c>
-      <c r="F8" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -643,7 +609,6 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -657,7 +622,6 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
